--- a/it_forms/026_mobile_loyalty_app_testing_registration--it_forms.xlsx
+++ b/it_forms/026_mobile_loyalty_app_testing_registration--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_header</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>mobile_phone_type</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>What is your mobile phone type?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>available_days</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>How many available days are you willing to commit to testing?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,87 +589,87 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>availability</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mobile Loyalty App Testing Registration</t>
+          <t>Availability</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>test_group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Testing group</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>testing_status</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Testing status</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>device_type</t>
+          <t>participant_details</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>what_is_your_device</t>
+          <t>Participant details</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>available_days</t>
+          <t>participant_sign_ups</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>available_days</t>
+          <t>Participant sign-ups</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,110 +704,110 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>availability</t>
+          <t>test_results</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>availability</t>
+          <t>Test results</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>device_details</t>
+          <t>testing_start_date</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>device_details</t>
+          <t>Testing start date</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>participant_details</t>
+          <t>testing_end_date</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>participant_details</t>
+          <t>Testing end date</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>participant_sign_ups</t>
+          <t>testing_start_time</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>participant_sign_ups</t>
+          <t>Testing start time</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>test_results</t>
+          <t>testing_end_time</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>test_results</t>
+          <t>Testing end time</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,18 +819,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>additional_comments</t>
+          <t>testing_duration</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>additional_comments</t>
+          <t>Testing duration</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,18 +842,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>assigned_to</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>assigned_to</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,18 +865,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Additional comments</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,159 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>test_group</t>
+          <t>assigned_to</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>test_group</t>
+          <t>Assigned to</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>testing_status</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>testing_status</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>testing_start_date</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>testing_start_date</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>testing_end_date</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>testing_end_date</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>testing_start_time</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>testing_start_time</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>testing_end_time</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>testing_end_time</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>testing_duration</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>testing_duration</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1075,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1103,221 +965,153 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>mobile_phone_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'it_forms'}</t>
+          <t>android</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'IT Forms'}</t>
+          <t>Android</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>mobile_phone_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'other_forms'}</t>
+          <t>ios</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Other Forms'}</t>
+          <t>iOS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>mobile_phone_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'it_forms'}</t>
+          <t>windows</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'IT Forms'}</t>
+          <t>Windows</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>test_group_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'other_forms'}</t>
+          <t>testing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Other Forms'}</t>
+          <t>Testing</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>device_type_choices</t>
+          <t>test_group_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'android'}</t>
+          <t>quality_assurance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'android'}</t>
+          <t>Quality Assurance</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>device_type_choices</t>
+          <t>test_group_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'ios'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'ios'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>device_type_choices</t>
+          <t>testing_status_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'windows'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'windows'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>test_group_choices</t>
+          <t>testing_status_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'testing',_'label':_'testing'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Testing', 'label': 'Testing'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>test_group_choices</t>
+          <t>testing_status_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'quality_assurance',_'label':_'quality_assurance'}</t>
+          <t>on_hold</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Quality Assurance', 'label': 'Quality Assurance'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>test_group_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'other',_'label':_'other'}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'Other', 'label': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>testing_status_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'active'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'Active'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>testing_status_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'closed'}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'Closed'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>testing_status_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'on_hold'}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'On Hold'}</t>
+          <t>On Hold</t>
         </is>
       </c>
     </row>
